--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6461,6 +6461,215 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132894827</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57142</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>668548</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6691834</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132894835</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106245</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>668570</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6691835</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -6573,7 +6573,7 @@
         <v>132894835</v>
       </c>
       <c r="B60" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -6573,7 +6573,7 @@
         <v>132894835</v>
       </c>
       <c r="B60" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125807887</v>
+        <v>127382928</v>
       </c>
       <c r="B2" t="n">
-        <v>4778</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668279</v>
+        <v>668350</v>
       </c>
       <c r="R2" t="n">
-        <v>6691905</v>
+        <v>6691894</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,48 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125853673</v>
+        <v>128260535</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668269</v>
+        <v>668565</v>
       </c>
       <c r="R3" t="n">
-        <v>6691918</v>
+        <v>6691734</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,60 +872,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125855915</v>
+        <v>128344121</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668328</v>
+        <v>668591</v>
       </c>
       <c r="R4" t="n">
-        <v>6691847</v>
+        <v>6691688</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,60 +969,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125855908</v>
+        <v>128953964</v>
       </c>
       <c r="B5" t="n">
-        <v>105396</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668294</v>
+        <v>668670</v>
       </c>
       <c r="R5" t="n">
-        <v>6691884</v>
+        <v>6691735</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1062,26 +1062,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127382963</v>
+        <v>128953965</v>
       </c>
       <c r="B6" t="n">
-        <v>92660</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668299</v>
+        <v>668636</v>
       </c>
       <c r="R6" t="n">
-        <v>6691892</v>
+        <v>6691635</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1143,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127382928</v>
+        <v>128953966</v>
       </c>
       <c r="B7" t="n">
-        <v>96722</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668350</v>
+        <v>668642</v>
       </c>
       <c r="R7" t="n">
-        <v>6691894</v>
+        <v>6691647</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1240,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1256,21 +1271,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,32 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128260564</v>
+        <v>128953967</v>
       </c>
       <c r="B8" t="n">
-        <v>91039</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5747</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,13 +1322,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668588</v>
+        <v>668642</v>
       </c>
       <c r="R8" t="n">
-        <v>6691696</v>
+        <v>6691649</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128260549</v>
+        <v>128953968</v>
       </c>
       <c r="B9" t="n">
-        <v>92820</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668507</v>
+        <v>668638</v>
       </c>
       <c r="R9" t="n">
-        <v>6691854</v>
+        <v>6691670</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1465,11 +1465,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1486,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260539</v>
+        <v>128953987</v>
       </c>
       <c r="B10" t="n">
-        <v>56907</v>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,42 +1492,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668536</v>
+        <v>668638</v>
       </c>
       <c r="R10" t="n">
-        <v>6691824</v>
+        <v>6691674</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,17 +1546,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Balgrop med fjädrar</t>
+          <t>Mycket örtrikt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1575,8 +1565,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1593,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260575</v>
+        <v>128344137</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>93199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,46 +1615,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668568</v>
+        <v>668567</v>
       </c>
       <c r="R11" t="n">
-        <v>6691681</v>
+        <v>6691956</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,60 +1689,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128260592</v>
+        <v>128344122</v>
       </c>
       <c r="B12" t="n">
-        <v>100820</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668587</v>
+        <v>668359</v>
       </c>
       <c r="R12" t="n">
-        <v>6691690</v>
+        <v>6691742</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,6 +1772,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1784,44 +1791,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260583</v>
+        <v>128953971</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,13 +1838,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668540</v>
+        <v>668680</v>
       </c>
       <c r="R13" t="n">
-        <v>6691905</v>
+        <v>6691646</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1861,12 +1868,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260581</v>
+        <v>128953993</v>
       </c>
       <c r="B14" t="n">
-        <v>4779</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,13 +1950,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668437</v>
+        <v>668664</v>
       </c>
       <c r="R14" t="n">
-        <v>6691726</v>
+        <v>6691742</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1973,12 +1980,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128260558</v>
+        <v>128953972</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,13 +2062,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668442</v>
+        <v>668638</v>
       </c>
       <c r="R15" t="n">
-        <v>6691699</v>
+        <v>6691675</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2085,12 +2092,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,6 +2108,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2117,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128260593</v>
+        <v>128344130</v>
       </c>
       <c r="B16" t="n">
-        <v>100820</v>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,37 +2150,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668593</v>
+        <v>668494</v>
       </c>
       <c r="R16" t="n">
-        <v>6691674</v>
+        <v>6691650</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2202,60 +2224,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128260565</v>
+        <v>128344131</v>
       </c>
       <c r="B17" t="n">
-        <v>91039</v>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5747</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668592</v>
+        <v>668602</v>
       </c>
       <c r="R17" t="n">
         <v>6691678</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2299,65 +2321,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128260540</v>
+        <v>128344132</v>
       </c>
       <c r="B18" t="n">
-        <v>57876</v>
+        <v>91680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668462</v>
+        <v>668568</v>
       </c>
       <c r="R18" t="n">
-        <v>6691745</v>
+        <v>6691712</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2401,68 +2418,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128260541</v>
+        <v>128344133</v>
       </c>
       <c r="B19" t="n">
-        <v>57876</v>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668559</v>
+        <v>668580</v>
       </c>
       <c r="R19" t="n">
-        <v>6691737</v>
+        <v>6691920</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2506,22 +2515,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128260548</v>
+        <v>128953979</v>
       </c>
       <c r="B20" t="n">
-        <v>92439</v>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2538,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,13 +2562,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668572</v>
+        <v>668636</v>
       </c>
       <c r="R20" t="n">
-        <v>6691927</v>
+        <v>6691609</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2583,12 +2592,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2615,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128260578</v>
+        <v>128344134</v>
       </c>
       <c r="B21" t="n">
-        <v>91522</v>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,37 +2635,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668571</v>
+        <v>668502</v>
       </c>
       <c r="R21" t="n">
-        <v>6691943</v>
+        <v>6691868</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2688,6 +2697,11 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2696,63 +2710,48 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128260582</v>
+        <v>128260557</v>
       </c>
       <c r="B22" t="n">
-        <v>4779</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2762,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668444</v>
+        <v>668414</v>
       </c>
       <c r="R22" t="n">
-        <v>6691724</v>
+        <v>6691754</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2808,21 +2807,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2839,14 +2823,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128260557</v>
+        <v>128260558</v>
       </c>
       <c r="B23" t="n">
-        <v>92806</v>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2874,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668414</v>
+        <v>668442</v>
       </c>
       <c r="R23" t="n">
-        <v>6691754</v>
+        <v>6691699</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2936,48 +2920,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128260577</v>
+        <v>128344129</v>
       </c>
       <c r="B24" t="n">
-        <v>105695</v>
+        <v>93209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668565</v>
+        <v>668557</v>
       </c>
       <c r="R24" t="n">
-        <v>6691734</v>
+        <v>6691949</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3021,22 +3005,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128260535</v>
+        <v>127382963</v>
       </c>
       <c r="B25" t="n">
-        <v>96878</v>
+        <v>93215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3044,21 +3028,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3068,13 +3052,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668565</v>
+        <v>668299</v>
       </c>
       <c r="R25" t="n">
-        <v>6691734</v>
+        <v>6691892</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3098,12 +3082,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3130,10 +3114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128344138</v>
+        <v>128260548</v>
       </c>
       <c r="B26" t="n">
-        <v>105699</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3141,37 +3125,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668564</v>
+        <v>668572</v>
       </c>
       <c r="R26" t="n">
-        <v>6691753</v>
+        <v>6691927</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3215,22 +3199,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128344142</v>
+        <v>128344126</v>
       </c>
       <c r="B27" t="n">
-        <v>98553</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3238,21 +3222,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3262,10 +3246,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668540</v>
+        <v>668368</v>
       </c>
       <c r="R27" t="n">
-        <v>6691947</v>
+        <v>6691735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128344132</v>
+        <v>128344127</v>
       </c>
       <c r="B28" t="n">
-        <v>91281</v>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3319,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3343,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668568</v>
+        <v>668594</v>
       </c>
       <c r="R28" t="n">
-        <v>6691712</v>
+        <v>6691661</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,10 +3405,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128344131</v>
+        <v>128953969</v>
       </c>
       <c r="B29" t="n">
-        <v>91281</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,37 +3416,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668602</v>
+        <v>668650</v>
       </c>
       <c r="R29" t="n">
-        <v>6691678</v>
+        <v>6691679</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3486,12 +3470,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3506,22 +3490,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128344123</v>
+        <v>128953970</v>
       </c>
       <c r="B30" t="n">
-        <v>104104</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,37 +3513,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222412</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668604</v>
+        <v>668676</v>
       </c>
       <c r="R30" t="n">
-        <v>6691663</v>
+        <v>6691606</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3583,12 +3567,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,26 +3583,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128344121</v>
+        <v>128260549</v>
       </c>
       <c r="B31" t="n">
-        <v>96882</v>
+        <v>93223</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,37 +3625,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668591</v>
+        <v>668507</v>
       </c>
       <c r="R31" t="n">
-        <v>6691688</v>
+        <v>6691854</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3696,64 +3695,69 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128344129</v>
+        <v>128260564</v>
       </c>
       <c r="B32" t="n">
-        <v>92810</v>
+        <v>91435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>5747</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668557</v>
+        <v>668588</v>
       </c>
       <c r="R32" t="n">
-        <v>6691949</v>
+        <v>6691696</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3797,60 +3801,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128344127</v>
+        <v>128260565</v>
       </c>
       <c r="B33" t="n">
-        <v>92443</v>
+        <v>91435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668594</v>
+        <v>668592</v>
       </c>
       <c r="R33" t="n">
-        <v>6691661</v>
+        <v>6691678</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3894,22 +3898,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344136</v>
+        <v>128953983</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>91435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,37 +3921,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5747</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668558</v>
+        <v>668689</v>
       </c>
       <c r="R34" t="n">
-        <v>6691675</v>
+        <v>6691641</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3971,17 +3975,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3996,22 +3995,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128344134</v>
+        <v>127382931</v>
       </c>
       <c r="B35" t="n">
-        <v>92790</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4019,37 +4018,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668502</v>
+        <v>668378</v>
       </c>
       <c r="R35" t="n">
-        <v>6691868</v>
+        <v>6691942</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4073,17 +4072,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4094,26 +4088,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128344130</v>
+        <v>128953977</v>
       </c>
       <c r="B36" t="n">
-        <v>91281</v>
+        <v>80336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4121,37 +4130,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668494</v>
+        <v>668697</v>
       </c>
       <c r="R36" t="n">
-        <v>6691650</v>
+        <v>6691561</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4175,12 +4187,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4189,28 +4201,44 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128344133</v>
+        <v>128953978</v>
       </c>
       <c r="B37" t="n">
-        <v>91281</v>
+        <v>80336</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,37 +4246,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3215</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668580</v>
+        <v>668684</v>
       </c>
       <c r="R37" t="n">
-        <v>6691920</v>
+        <v>6691557</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4272,12 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4288,26 +4316,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128344139</v>
+        <v>128953973</v>
       </c>
       <c r="B38" t="n">
-        <v>4779</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,37 +4358,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668595</v>
+        <v>668704</v>
       </c>
       <c r="R38" t="n">
-        <v>6691931</v>
+        <v>6691768</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4369,12 +4417,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4389,57 +4437,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128953971</v>
+        <v>128953974</v>
       </c>
       <c r="B39" t="n">
-        <v>91550</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668680</v>
+        <v>668675</v>
       </c>
       <c r="R39" t="n">
-        <v>6691646</v>
+        <v>6691565</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4482,21 +4535,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4513,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128953999</v>
+        <v>128260539</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4524,37 +4562,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668676</v>
+        <v>668536</v>
       </c>
       <c r="R40" t="n">
-        <v>6691605</v>
+        <v>6691824</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4578,12 +4621,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Balgrop med fjädrar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4592,24 +4640,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4626,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128953970</v>
+        <v>132894827</v>
       </c>
       <c r="B41" t="n">
-        <v>91514</v>
+        <v>57162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4637,34 +4669,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668676</v>
+        <v>668548</v>
       </c>
       <c r="R41" t="n">
-        <v>6691606</v>
+        <v>6691834</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4691,12 +4728,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4707,21 +4749,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4738,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128953979</v>
+        <v>128953999</v>
       </c>
       <c r="B42" t="n">
-        <v>91323</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3215</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4773,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668636</v>
+        <v>668676</v>
       </c>
       <c r="R42" t="n">
-        <v>6691609</v>
+        <v>6691605</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4817,8 +4844,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4835,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128953969</v>
+        <v>125807887</v>
       </c>
       <c r="B43" t="n">
-        <v>91514</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4846,34 +4889,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668650</v>
+        <v>668279</v>
       </c>
       <c r="R43" t="n">
-        <v>6691679</v>
+        <v>6691905</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4900,12 +4943,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4916,6 +4959,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4932,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128953997</v>
+        <v>125807888</v>
       </c>
       <c r="B44" t="n">
-        <v>100913</v>
+        <v>4781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,34 +5001,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668641</v>
+        <v>668255</v>
       </c>
       <c r="R44" t="n">
-        <v>6691647</v>
+        <v>6691905</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4997,12 +5055,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5013,6 +5071,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5029,32 +5102,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128953968</v>
+        <v>127382960</v>
       </c>
       <c r="B45" t="n">
-        <v>96970</v>
+        <v>4781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5064,10 +5137,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668638</v>
+        <v>668228</v>
       </c>
       <c r="R45" t="n">
-        <v>6691670</v>
+        <v>6691916</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5094,12 +5167,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5110,6 +5183,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5126,10 +5214,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128953972</v>
+        <v>128260581</v>
       </c>
       <c r="B46" t="n">
-        <v>96070</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5137,21 +5225,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5161,13 +5249,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668638</v>
+        <v>668437</v>
       </c>
       <c r="R46" t="n">
-        <v>6691675</v>
+        <v>6691726</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5191,12 +5279,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5238,32 +5326,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128953967</v>
+        <v>128260582</v>
       </c>
       <c r="B47" t="n">
-        <v>96970</v>
+        <v>4781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5273,13 +5361,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668642</v>
+        <v>668444</v>
       </c>
       <c r="R47" t="n">
-        <v>6691649</v>
+        <v>6691724</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5303,12 +5391,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5319,6 +5407,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5335,32 +5438,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128953964</v>
+        <v>128260583</v>
       </c>
       <c r="B48" t="n">
-        <v>96970</v>
+        <v>4781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5370,13 +5473,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668670</v>
+        <v>668540</v>
       </c>
       <c r="R48" t="n">
-        <v>6691735</v>
+        <v>6691905</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5400,12 +5503,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5419,17 +5522,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5447,48 +5550,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128953965</v>
+        <v>128344139</v>
       </c>
       <c r="B49" t="n">
-        <v>96970</v>
+        <v>4781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668636</v>
+        <v>668595</v>
       </c>
       <c r="R49" t="n">
-        <v>6691635</v>
+        <v>6691931</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5512,12 +5615,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5532,22 +5635,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128953966</v>
+        <v>128260540</v>
       </c>
       <c r="B50" t="n">
-        <v>96970</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5555,37 +5658,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668642</v>
+        <v>668462</v>
       </c>
       <c r="R50" t="n">
-        <v>6691647</v>
+        <v>6691745</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5609,12 +5717,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5641,48 +5749,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128953994</v>
+        <v>128260541</v>
       </c>
       <c r="B51" t="n">
-        <v>100913</v>
+        <v>58114</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668674</v>
+        <v>668559</v>
       </c>
       <c r="R51" t="n">
-        <v>6691735</v>
+        <v>6691737</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5706,12 +5822,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5738,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128953987</v>
+        <v>125853673</v>
       </c>
       <c r="B52" t="n">
-        <v>96166</v>
+        <v>99035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5749,37 +5865,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>210</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668638</v>
+        <v>668269</v>
       </c>
       <c r="R52" t="n">
-        <v>6691674</v>
+        <v>6691918</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5803,17 +5919,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mycket örtrikt</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5822,49 +5933,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128953996</v>
+        <v>125855915</v>
       </c>
       <c r="B53" t="n">
-        <v>100913</v>
+        <v>99035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5872,37 +5962,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668650</v>
+        <v>668328</v>
       </c>
       <c r="R53" t="n">
-        <v>6691592</v>
+        <v>6691847</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5926,12 +6016,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5946,22 +6036,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128953998</v>
+        <v>128344142</v>
       </c>
       <c r="B54" t="n">
-        <v>100913</v>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5969,37 +6059,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668653</v>
+        <v>668540</v>
       </c>
       <c r="R54" t="n">
-        <v>6691655</v>
+        <v>6691947</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6023,12 +6113,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6043,50 +6133,54 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128953973</v>
+        <v>128260575</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6095,13 +6189,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668704</v>
+        <v>668568</v>
       </c>
       <c r="R55" t="n">
-        <v>6691768</v>
+        <v>6691681</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6125,12 +6219,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6157,48 +6251,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128953993</v>
+        <v>128344136</v>
       </c>
       <c r="B56" t="n">
-        <v>92200</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668664</v>
+        <v>668558</v>
       </c>
       <c r="R56" t="n">
-        <v>6691742</v>
+        <v>6691675</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6222,12 +6316,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6238,41 +6337,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128953995</v>
+        <v>125855908</v>
       </c>
       <c r="B57" t="n">
-        <v>100913</v>
+        <v>106244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6280,37 +6364,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668644</v>
+        <v>668294</v>
       </c>
       <c r="R57" t="n">
-        <v>6691674</v>
+        <v>6691884</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6334,12 +6418,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6354,44 +6438,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128953983</v>
+        <v>128260577</v>
       </c>
       <c r="B58" t="n">
-        <v>91085</v>
+        <v>106244</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6401,13 +6485,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668689</v>
+        <v>668565</v>
       </c>
       <c r="R58" t="n">
-        <v>6691641</v>
+        <v>6691734</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6431,12 +6515,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6463,10 +6547,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132894827</v>
+        <v>128344138</v>
       </c>
       <c r="B59" t="n">
-        <v>57145</v>
+        <v>106244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,42 +6558,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668548</v>
+        <v>668564</v>
       </c>
       <c r="R59" t="n">
-        <v>6691834</v>
+        <v>6691753</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6533,17 +6612,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6558,12 +6632,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6573,7 +6647,7 @@
         <v>132894835</v>
       </c>
       <c r="B60" t="n">
-        <v>106260</v>
+        <v>106324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6669,6 +6743,894 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128344123</v>
+      </c>
+      <c r="B61" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>668604</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6691663</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128260592</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>668587</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6691690</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128260593</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>668593</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6691674</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128953994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>668674</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6691735</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128953995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>668644</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6691674</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128953996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>668650</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6691592</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128953997</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>668641</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6691647</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128953998</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>668653</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6691655</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128953986</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>668686</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6691559</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382928</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260535</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344121</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953965</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953967</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953987</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344122</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953971</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,6 +2089,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953993</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2206,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953972</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2233,6 +2308,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344130</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2330,6 +2410,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344131</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2427,6 +2512,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344132</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344133</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953979</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +2823,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344134</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260557</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2917,6 +3027,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260558</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3014,6 +3129,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344129</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3111,6 +3231,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382963</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3208,6 +3333,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260548</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3305,6 +3435,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344126</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344127</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3499,6 +3639,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953969</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3611,6 +3756,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953970</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3713,6 +3863,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260549</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3810,6 +3965,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260564</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3907,6 +4067,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260565</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4004,6 +4169,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953983</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4116,6 +4286,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382931</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4232,6 +4407,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953977</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953978</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953973</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953974</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4655,6 +4850,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260539</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4762,6 +4962,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894827</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4875,6 +5080,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953999</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4987,6 +5197,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807887</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5099,6 +5314,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807888</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5211,6 +5431,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382960</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5323,6 +5548,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260581</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5435,6 +5665,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260582</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5547,6 +5782,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260583</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5644,6 +5884,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344139</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5746,6 +5991,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260540</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5851,6 +6101,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260541</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5948,6 +6203,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853673</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6045,6 +6305,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855915</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6142,6 +6407,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344142</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6248,6 +6518,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260575</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6350,6 +6625,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344136</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6447,6 +6727,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855908</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6544,6 +6829,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260577</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6641,6 +6931,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344138</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6743,6 +7038,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894835</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6840,6 +7140,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344123</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6937,6 +7242,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260592</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7034,6 +7344,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260593</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7131,6 +7446,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953994</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7228,6 +7548,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953995</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7325,6 +7650,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953996</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7422,6 +7752,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953997</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7519,6 +7854,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953998</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7631,8 +7971,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>